--- a/División/RUN_División.xlsx
+++ b/División/RUN_División.xlsx
@@ -431,13 +431,13 @@
         <v>31.05379528768682</v>
       </c>
       <c r="C2" s="2">
-        <v>115.8112917710915</v>
+        <v>115.79119381048</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="2">
-        <v>35.96380146662046</v>
+        <v>35.95756028707515</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -445,7 +445,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="2">
-        <v>33.00679589111741</v>
+        <v>33.0067958911174</v>
       </c>
       <c r="C3" s="2">
         <v>109.9883045323912</v>
@@ -479,7 +479,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="2">
-        <v>23.51244717031737</v>
+        <v>23.51244717031736</v>
       </c>
       <c r="C5" s="2">
         <v>113.3627282107537</v>
